--- a/research_evaluation_20261030/results/mainflow_results.xlsx
+++ b/research_evaluation_20261030/results/mainflow_results.xlsx
@@ -491,41 +491,65 @@
           <t>off</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="I2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="L2" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="M2" t="n">
-        <v>67.19999999999999</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.826</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.346</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.955</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>66.9</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -534,41 +558,65 @@
           <t>on</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>50</v>
-      </c>
-      <c r="C3" t="n">
-        <v>45</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>27</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="L3" t="n">
-        <v>44</v>
-      </c>
-      <c r="M3" t="n">
-        <v>67.19999999999999</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.775</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.955</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -709,8 +757,10 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="b">
-        <v>0</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -723,28 +773,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>32</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>a3:v1000000:r1000023:block:1001491:1:0</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="R2" t="n">
-        <v>50.4</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>70.1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -779,8 +842,10 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="b">
-        <v>0</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -793,28 +858,41 @@
           <t>E1|E2|E34|E13</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>36</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>a3:v1000000:r1000023:block:1001506:1:0</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>61</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -849,8 +927,10 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="b">
-        <v>0</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -863,28 +943,41 @@
           <t>E1|E11</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>46</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>a3:v1000000:r1000023:block:1001506:1:0</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>102.4</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>102.4</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -919,8 +1012,10 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="b">
-        <v>0</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -934,31 +1029,45 @@
           <t>E2</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>36</v>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001558:1:0</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>130</v>
-      </c>
-      <c r="R5" t="n">
-        <v>29.5</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -993,8 +1102,10 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="b">
-        <v>0</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1007,31 +1118,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>29</v>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001547:1:0|a3:v1000001:r1000024:block:1001562:1:0|a3:v1000001:r1000024:block:1001563:1:0</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>27.3</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1066,8 +1191,10 @@
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="b">
-        <v>0</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1081,31 +1208,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>34</v>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001558:1:0</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>30.7</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1136,45 +1277,60 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>response_rejected</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+          <t>generated</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>33</v>
+          <t>Khi điều chỉnh khe hở bugi Iridium Power, dụng cụ không được chạm vào Iridium Center Electrode hoặc Porcelain. Dụng cụ cần kiểm tra lại bằng một dụng cụ gapping tool đã được校准.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>E3|E32</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>a3:v1000002:r1000035:block:1002153:1:0|a3:v1000002:r1000035:block:1002154:1:0</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>59.8</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>37.8</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1209,8 +1365,10 @@
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="b">
-        <v>0</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1223,31 +1381,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>21</v>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>a3:v1000002:r1000035:block:1002158:1:0|a3:v1000002:r1000035:block:1002175:1:0</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="R9" t="n">
-        <v>62</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1282,8 +1454,10 @@
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="b">
-        <v>0</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1295,31 +1469,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>49</v>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>a3:v1000002:r1000035:block:1002175:1:0</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="R10" t="n">
-        <v>90.90000000000001</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>84.1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>90.9</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1354,8 +1542,10 @@
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="b">
-        <v>0</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1367,31 +1557,45 @@
           <t>E18|E20</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>22</v>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>a3:v1000003:r1000036:block:1002271:1:0|a3:v1000003:r1000036:block:1002290:1:0</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>47.4</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>113.1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1426,8 +1630,10 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="b">
-        <v>0</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1439,28 +1645,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>16</v>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>a3:v1000003:r1000036:block:1002281:1:0</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>12.5</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1495,8 +1714,10 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="b">
-        <v>0</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1510,31 +1731,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>22</v>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>a3:v1000004:r1000037:block:1002404:1:0</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>43.3</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>43.3</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1569,8 +1804,10 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="b">
-        <v>0</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1583,31 +1820,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>32</v>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>a3:v1000004:r1000037:block:1002409:1:0</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="R14" t="n">
-        <v>16.8</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>70.9</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1642,8 +1893,10 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="b">
-        <v>0</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1655,28 +1908,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>38</v>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>a3:v1000005:r1000038:block:1002512:1:0</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>48.1</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>48.1</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1711,8 +1977,10 @@
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="b">
-        <v>0</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1725,28 +1993,41 @@
           <t>E5</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>22</v>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>a3:v1000005:r1000038:block:1002516:1:0</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="R16" t="n">
-        <v>22.3</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1781,8 +2062,10 @@
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="b">
-        <v>0</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1794,28 +2077,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>26</v>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>a3:v1000006:r1000032:block:1002023:1:0</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>37.2</v>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>34.4</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>37.2</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1850,8 +2146,10 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="b">
-        <v>0</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1864,28 +2162,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>32</v>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>a3:v1000006:r1000032:block:1002024:1:0</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>84.40000000000001</v>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>84.4</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1920,8 +2231,10 @@
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="b">
-        <v>0</v>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1934,28 +2247,41 @@
           <t>E7</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>26</v>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>a3:v1000007:r1000039:block:1002594:1:0</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>107.9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>40.8</v>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>107.9</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1990,8 +2316,10 @@
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="b">
-        <v>0</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2003,28 +2331,41 @@
           <t>E4</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>20</v>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>a3:v1000007:r1000039:block:1002595:1:0</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>41.2</v>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2059,8 +2400,10 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="b">
-        <v>0</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2072,28 +2415,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>48</v>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>a3:v1000007:r1000039:block:1002597:1:0</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="R21" t="n">
-        <v>145.5</v>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>71.6</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2128,8 +2484,10 @@
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="b">
-        <v>0</v>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2141,28 +2499,41 @@
           <t>E1|E13</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>45</v>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>a3:v1000008:r1000075:block:1003068:1:0|a3:v1000008:r1000075:block:1003069:1:0</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>123.8</v>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>123.8</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2197,8 +2568,10 @@
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="b">
-        <v>0</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2211,28 +2584,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>54</v>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>a3:v1000008:r1000075:block:1003070:1:0</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>144.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>105.8</v>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>105.8</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2267,8 +2653,10 @@
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="b">
-        <v>0</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2280,28 +2668,41 @@
           <t>E2</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>19</v>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>a3:v1000009:r1000040:block:1002688:1:0|a3:v1000009:r1000040:block:1002689:1:0</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>127.4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>21.9</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>127.4</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2336,8 +2737,10 @@
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="b">
-        <v>0</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2350,31 +2753,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>28</v>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>a3:v1000009:r1000040:block:1002697:1:0</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>49.9</v>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2409,8 +2826,10 @@
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="b">
-        <v>0</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2424,31 +2843,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>48</v>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>a3:v1000009:r1000040:block:1002698:1:0</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="R26" t="n">
-        <v>135</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2483,8 +2916,10 @@
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="b">
-        <v>0</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2497,28 +2932,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>31</v>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>a3:v1000010:r1000076:block:1003166:1:0</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>141.9</v>
-      </c>
-      <c r="R27" t="n">
-        <v>58.9</v>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>141.9</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2553,8 +3001,10 @@
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="b">
-        <v>0</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2567,28 +3017,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>30</v>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>a3:v1000010:r1000076:block:1003173:1:0</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="R28" t="n">
-        <v>48.8</v>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2623,8 +3086,10 @@
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="b">
-        <v>0</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2636,31 +3101,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>28</v>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>a3:v1000011:r1000025:block:1001588:1:0</t>
         </is>
       </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>12.6</v>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2695,8 +3174,10 @@
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="b">
-        <v>0</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2708,28 +3189,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>21</v>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>a3:v1000011:r1000025:block:1001605:1:0|a3:v1000011:r1000025:block:1001606:1:0</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>11</v>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2764,8 +3258,10 @@
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="b">
-        <v>0</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2778,28 +3274,41 @@
           <t>E3|E7|E1|E5|E8</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>38</v>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>a3:v1000012:r1000026:block:1001645:1:0|a3:v1000012:r1000026:block:1001646:1:0|a3:v1000012:r1000026:block:1001647:1:0</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>99.90000000000001</v>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>35.2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>99.9</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2834,8 +3343,10 @@
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="b">
-        <v>0</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2847,28 +3358,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>19</v>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>a3:v1000012:r1000026:block:1001654:1:0</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>101</v>
-      </c>
-      <c r="R32" t="n">
-        <v>8.5</v>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2903,8 +3427,10 @@
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="b">
-        <v>0</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2916,28 +3442,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>18</v>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>a3:v1000013:r1000022:block:1001429:1:0</t>
         </is>
       </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R33" t="n">
-        <v>8.199999999999999</v>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2972,8 +3511,10 @@
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="b">
-        <v>0</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2986,28 +3527,41 @@
           <t>E3|E4</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>46</v>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>a3:v1000013:r1000022:block:1001431:1:0|a3:v1000013:r1000022:block:1001432:1:0|a3:v1000013:r1000022:block:1001433:1:0</t>
         </is>
       </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>60.4</v>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>33.1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -3042,8 +3596,10 @@
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="b">
-        <v>0</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3056,31 +3612,45 @@
           <t>E3|E1</t>
         </is>
       </c>
-      <c r="K35" t="n">
-        <v>25</v>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>a3:v1000014:r1000084:block:1003639:1:0|a3:v1000014:r1000084:block:1003642:1:0</t>
         </is>
       </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="R35" t="n">
-        <v>43.7</v>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>84.1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>43.7</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -3115,8 +3685,10 @@
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="b">
-        <v>0</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3129,28 +3701,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>27</v>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>a3:v1000014:r1000084:block:1003662:1:0</t>
         </is>
       </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>66.8</v>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>64.3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>66.8</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3185,8 +3770,10 @@
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="b">
-        <v>0</v>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3199,31 +3786,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>25</v>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001808:1:0</t>
         </is>
       </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="R37" t="n">
-        <v>14.6</v>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3258,8 +3859,10 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="b">
-        <v>0</v>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3273,31 +3876,45 @@
           <t>E3</t>
         </is>
       </c>
-      <c r="K38" t="n">
-        <v>20</v>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001808:1:0|a3:v1000015:r1000028:block:1001810:1:0</t>
         </is>
       </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="R38" t="n">
-        <v>17.5</v>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -3332,8 +3949,10 @@
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="b">
-        <v>0</v>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3347,31 +3966,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>77</v>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001793:1:0</t>
         </is>
       </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>170.7</v>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>170.7</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -3406,8 +4039,10 @@
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="b">
-        <v>0</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3420,31 +4055,45 @@
           <t>E2</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>26</v>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>a3:v1000016:r1000029:block:1001835:1:0|a3:v1000016:r1000029:block:1001836:1:0</t>
         </is>
       </c>
-      <c r="M40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>4</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>174.4</v>
-      </c>
-      <c r="R40" t="n">
-        <v>15.6</v>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>174.4</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -3479,8 +4128,10 @@
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="b">
-        <v>0</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3493,28 +4144,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K41" t="n">
-        <v>16</v>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>a3:v1000016:r1000029:block:1001851:1:0</t>
         </is>
       </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="R41" t="n">
-        <v>18.6</v>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3549,8 +4213,10 @@
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="b">
-        <v>0</v>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3563,28 +4229,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>30</v>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>a3:v1000016:r1000029:block:1001849:1:0</t>
         </is>
       </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>40</v>
-      </c>
-      <c r="R42" t="n">
-        <v>69</v>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3619,8 +4298,10 @@
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="b">
-        <v>0</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3634,31 +4315,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K43" t="n">
-        <v>20</v>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>a3:v1000017:r1000081:block:1003443:1:0</t>
         </is>
       </c>
-      <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="R43" t="n">
-        <v>19</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3693,8 +4388,10 @@
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="b">
-        <v>0</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3706,31 +4403,45 @@
           <t>E1|E3</t>
         </is>
       </c>
-      <c r="K44" t="n">
-        <v>23</v>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>a3:v1000017:r1000081:block:1003450:1:0</t>
         </is>
       </c>
-      <c r="M44" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="R44" t="n">
-        <v>14.7</v>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3765,8 +4476,10 @@
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="b">
-        <v>0</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3778,31 +4491,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K45" t="n">
-        <v>20</v>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>a3:v1000017:r1000081:block:1003483:1:0|a3:v1000017:r1000081:block:1003487:1:0</t>
         </is>
       </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="R45" t="n">
-        <v>14.3</v>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>39.2</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -3837,8 +4564,10 @@
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="b">
-        <v>0</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3852,31 +4581,45 @@
           <t>E1|E2|E3|E5|E9</t>
         </is>
       </c>
-      <c r="K46" t="n">
-        <v>60</v>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>a3:v1000018:r1000031:block:1001991:1:0</t>
         </is>
       </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>136.9</v>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>136.9</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3911,8 +4654,10 @@
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="b">
-        <v>0</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3925,28 +4670,41 @@
           <t>E1|E2</t>
         </is>
       </c>
-      <c r="K47" t="n">
-        <v>41</v>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>a3:v1000018:r1000031:block:1001959:1:0|a3:v1000018:r1000031:block:1001978:1:0</t>
         </is>
       </c>
-      <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="R47" t="n">
-        <v>122.2</v>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>147.4</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>122.2</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3977,45 +4735,65 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>gateway_unavailable</t>
-        </is>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
+          <t>generated</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="n">
-        <v>9</v>
+          <t>Chiều dài 14 inch tương đương 355 mm.
+Chiều dài 26 inch tương đương 650 mm.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>a3:v1000019:r1000041:block:1002799:1:0</t>
         </is>
       </c>
-      <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>140</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0.7</v>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -4046,45 +4824,64 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>gateway_unavailable</t>
-        </is>
-      </c>
-      <c r="H49" t="b">
-        <v>0</v>
+          <t>generated</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="n">
-        <v>12</v>
+          <t>Trong bảng Rear Wiper Blades, cỡ 12 inch/300 mm liệt kê các mã sản phẩm sau: Beam Wiper Blades.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>a3:v1000019:r1000041:block:1002805:1:0|a3:v1000019:r1000041:block:1002806:1:0</t>
         </is>
       </c>
-      <c r="M49" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>4</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.4</v>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>190.6</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -4115,45 +4912,70 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>gateway_unavailable</t>
-        </is>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
+          <t>generated</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="n">
-        <v>17</v>
+          <t>Tầm với của LPH-040A1 là 400mm.
+Tầm với của VS-050S2 là 520mm.
+Tải trọng tối đa của LPH-040A1 là 3kg.
+Tải trọng tối đa của VS-050S2 là 4kg.
+Chu kỳ của LPH-040A1 là 0.45sec.
+Chu kỳ của VS-050S2 là 0.35sec.
+Chu kỳ của LPH-040A1 và VS-050S2 không thể được so sánh ở cùng tải.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>E2|E5</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001808:1:0|a3:v1000015:r1000028:block:1001810:1:0|a3:v1000017:r1000081:block:1003483:1:0|a3:v1000017:r1000081:block:1003484:1:0</t>
         </is>
       </c>
-      <c r="M50" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0.6</v>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -4184,45 +5006,65 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>gateway_unavailable</t>
-        </is>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
+          <t>generated</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="n">
-        <v>34</v>
+          <t>RC8A đóng vai trò như một loại hộp bảo vệ cho bộ điều khiển robot, giúp bảo vệ bộ điều khiển khỏi môi trường khắc nghiệt. Trong tài liệu Dual-arm Control, RC8A được mô tả là phù hợp với các loại robot HSR và HS-A1, đặc biệt là những robot có tốc độ cao và độ chính xác cao, rất lý tưởng cho các cơ sở có thời gian chu kỳ ngắn.
+Tên robot tương thích với Dual-arm Control là HS Series/HS-A1 Series. Trong tài liệu Dual-arm Control, nó được mô tả là phù hợp với các loại robot HSR và HS-A1, đặc biệt là những robot có tốc độ cao và độ chính xác cao, rất lý tưởng cho các cơ sở có thời gian chu kỳ ngắn.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>E2|E3|E1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001545:1:0|a3:v1000001:r1000024:block:1001546:1:0|a3:v1000014:r1000084:block:1003639:1:0</t>
         </is>
       </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.5</v>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>67.6</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -4257,8 +5099,10 @@
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="b">
-        <v>1</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -4271,28 +5115,41 @@
           <t>E1|E27</t>
         </is>
       </c>
-      <c r="K52" t="n">
-        <v>32</v>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>a3:v1000000:r1000023:block:1001491:1:0</t>
         </is>
       </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="R52" t="n">
-        <v>55.3</v>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>70.1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -4327,8 +5184,10 @@
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="b">
-        <v>1</v>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4340,28 +5199,41 @@
           <t>E1|E2|E3|E4</t>
         </is>
       </c>
-      <c r="K53" t="n">
-        <v>36</v>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>a3:v1000000:r1000023:block:1001506:1:0</t>
         </is>
       </c>
-      <c r="M53" t="n">
-        <v>1</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="R53" t="n">
-        <v>55</v>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -4396,8 +5268,10 @@
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="b">
-        <v>1</v>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4410,28 +5284,41 @@
           <t>E1|E12</t>
         </is>
       </c>
-      <c r="K54" t="n">
-        <v>46</v>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>a3:v1000000:r1000023:block:1001506:1:0</t>
         </is>
       </c>
-      <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="R54" t="n">
-        <v>100.1</v>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>100.1</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4466,8 +5353,10 @@
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="b">
-        <v>0</v>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4481,31 +5370,45 @@
           <t>E2</t>
         </is>
       </c>
-      <c r="K55" t="n">
-        <v>36</v>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001558:1:0</t>
         </is>
       </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>130</v>
-      </c>
-      <c r="R55" t="n">
-        <v>29.5</v>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4540,8 +5443,10 @@
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="b">
-        <v>0</v>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4554,31 +5459,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K56" t="n">
-        <v>29</v>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001547:1:0|a3:v1000001:r1000024:block:1001562:1:0|a3:v1000001:r1000024:block:1001563:1:0</t>
         </is>
       </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>3</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P56" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="R56" t="n">
-        <v>27.3</v>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -4613,8 +5532,10 @@
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="b">
-        <v>0</v>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4628,31 +5549,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K57" t="n">
-        <v>34</v>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001558:1:0</t>
         </is>
       </c>
-      <c r="M57" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" t="n">
-        <v>5</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="R57" t="n">
-        <v>30.7</v>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -4691,8 +5626,10 @@
           <t>response_rejected</t>
         </is>
       </c>
-      <c r="H58" t="b">
-        <v>1</v>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4700,28 +5637,41 @@
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="n">
-        <v>33</v>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>a3:v1000002:r1000035:block:1002153:1:0|a3:v1000002:r1000035:block:1002154:1:0</t>
         </is>
       </c>
-      <c r="M58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>64.59999999999999</v>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>46.6</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4756,8 +5706,10 @@
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="b">
-        <v>1</v>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4770,31 +5722,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K59" t="n">
-        <v>21</v>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>a3:v1000002:r1000035:block:1002158:1:0|a3:v1000002:r1000035:block:1002175:1:0</t>
         </is>
       </c>
-      <c r="M59" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N59" t="n">
-        <v>4</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="R59" t="n">
-        <v>62.1</v>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>62.1</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4829,8 +5795,10 @@
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="b">
-        <v>1</v>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4843,31 +5811,45 @@
           <t>E40</t>
         </is>
       </c>
-      <c r="K60" t="n">
-        <v>49</v>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>a3:v1000002:r1000035:block:1002175:1:0</t>
         </is>
       </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="R60" t="n">
-        <v>98.40000000000001</v>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>84.1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>98.4</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4902,8 +5884,10 @@
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="b">
-        <v>1</v>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4915,31 +5899,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K61" t="n">
-        <v>22</v>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>a3:v1000003:r1000036:block:1002271:1:0|a3:v1000003:r1000036:block:1002290:1:0</t>
         </is>
       </c>
-      <c r="M61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>3</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>46.1</v>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>113.1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -4974,8 +5972,10 @@
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="b">
-        <v>0</v>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4987,28 +5987,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K62" t="n">
-        <v>16</v>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>a3:v1000003:r1000036:block:1002281:1:0</t>
         </is>
       </c>
-      <c r="M62" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="R62" t="n">
-        <v>12.5</v>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -5043,8 +6056,10 @@
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="b">
-        <v>1</v>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5058,31 +6073,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K63" t="n">
-        <v>22</v>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>a3:v1000004:r1000037:block:1002404:1:0</t>
         </is>
       </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="R63" t="n">
-        <v>43.6</v>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>43.6</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -5117,8 +6146,10 @@
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="b">
-        <v>0</v>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5131,31 +6162,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K64" t="n">
-        <v>32</v>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>a3:v1000004:r1000037:block:1002409:1:0</t>
         </is>
       </c>
-      <c r="M64" t="n">
-        <v>1</v>
-      </c>
-      <c r="N64" t="n">
-        <v>4</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="R64" t="n">
-        <v>16.8</v>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>70.9</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -5190,8 +6235,10 @@
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="b">
-        <v>0</v>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5203,28 +6250,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K65" t="n">
-        <v>38</v>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>a3:v1000005:r1000038:block:1002512:1:0</t>
         </is>
       </c>
-      <c r="M65" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="R65" t="n">
-        <v>48.2</v>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -5259,8 +6319,10 @@
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="b">
-        <v>0</v>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5273,28 +6335,41 @@
           <t>E5</t>
         </is>
       </c>
-      <c r="K66" t="n">
-        <v>22</v>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>a3:v1000005:r1000038:block:1002516:1:0</t>
         </is>
       </c>
-      <c r="M66" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="R66" t="n">
-        <v>22.3</v>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -5329,8 +6404,10 @@
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="b">
-        <v>1</v>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5342,28 +6419,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K67" t="n">
-        <v>26</v>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>a3:v1000006:r1000032:block:1002023:1:0</t>
         </is>
       </c>
-      <c r="M67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="R67" t="n">
-        <v>38.5</v>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>34.4</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -5398,8 +6488,10 @@
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="b">
-        <v>1</v>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5412,28 +6504,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K68" t="n">
-        <v>32</v>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>a3:v1000006:r1000032:block:1002024:1:0</t>
         </is>
       </c>
-      <c r="M68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="R68" t="n">
-        <v>84.3</v>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -5468,8 +6573,10 @@
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="b">
-        <v>1</v>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5482,28 +6589,41 @@
           <t>E7</t>
         </is>
       </c>
-      <c r="K69" t="n">
-        <v>26</v>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>a3:v1000007:r1000039:block:1002594:1:0</t>
         </is>
       </c>
-      <c r="M69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>107.9</v>
-      </c>
-      <c r="R69" t="n">
-        <v>42.7</v>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>107.9</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -5538,8 +6658,10 @@
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="b">
-        <v>1</v>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5551,28 +6673,41 @@
           <t>E4</t>
         </is>
       </c>
-      <c r="K70" t="n">
-        <v>20</v>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>a3:v1000007:r1000039:block:1002595:1:0</t>
         </is>
       </c>
-      <c r="M70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="R70" t="n">
-        <v>42.2</v>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>42.2</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -5607,8 +6742,10 @@
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="b">
-        <v>1</v>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5620,28 +6757,41 @@
           <t>E27</t>
         </is>
       </c>
-      <c r="K71" t="n">
-        <v>48</v>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>a3:v1000007:r1000039:block:1002597:1:0</t>
         </is>
       </c>
-      <c r="M71" t="n">
-        <v>1</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="R71" t="n">
-        <v>149.5</v>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>71.6</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>149.5</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -5676,8 +6826,10 @@
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="b">
-        <v>1</v>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5689,28 +6841,41 @@
           <t>E1|E13</t>
         </is>
       </c>
-      <c r="K72" t="n">
-        <v>45</v>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>a3:v1000008:r1000075:block:1003068:1:0|a3:v1000008:r1000075:block:1003069:1:0</t>
         </is>
       </c>
-      <c r="M72" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R72" t="n">
-        <v>123.6</v>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>123.6</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -5745,8 +6910,10 @@
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="b">
-        <v>1</v>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5759,28 +6926,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K73" t="n">
-        <v>54</v>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>a3:v1000008:r1000075:block:1003070:1:0</t>
         </is>
       </c>
-      <c r="M73" t="n">
-        <v>1</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>144.5</v>
-      </c>
-      <c r="R73" t="n">
-        <v>106.1</v>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>106.1</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -5815,8 +6995,10 @@
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="b">
-        <v>1</v>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5829,28 +7011,41 @@
           <t>E1|E2</t>
         </is>
       </c>
-      <c r="K74" t="n">
-        <v>19</v>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>a3:v1000009:r1000040:block:1002688:1:0|a3:v1000009:r1000040:block:1002689:1:0</t>
         </is>
       </c>
-      <c r="M74" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>127.4</v>
-      </c>
-      <c r="R74" t="n">
-        <v>24.3</v>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>127.4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -5885,8 +7080,10 @@
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="b">
-        <v>1</v>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5899,31 +7096,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K75" t="n">
-        <v>28</v>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>a3:v1000009:r1000040:block:1002697:1:0</t>
         </is>
       </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>2</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1</v>
-      </c>
-      <c r="P75" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="R75" t="n">
-        <v>50</v>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -5958,8 +7169,10 @@
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="b">
-        <v>1</v>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5971,31 +7184,45 @@
           <t>E1|E3|E21</t>
         </is>
       </c>
-      <c r="K76" t="n">
-        <v>48</v>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>a3:v1000009:r1000040:block:1002698:1:0</t>
         </is>
       </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>2</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="R76" t="n">
-        <v>122.2</v>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>122.2</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -6030,8 +7257,10 @@
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="b">
-        <v>1</v>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6044,28 +7273,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K77" t="n">
-        <v>31</v>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>a3:v1000010:r1000076:block:1003166:1:0</t>
         </is>
       </c>
-      <c r="M77" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>141.9</v>
-      </c>
-      <c r="R77" t="n">
-        <v>61.7</v>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>141.9</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -6100,8 +7342,10 @@
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="b">
-        <v>1</v>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6114,28 +7358,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K78" t="n">
-        <v>30</v>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>a3:v1000010:r1000076:block:1003173:1:0</t>
         </is>
       </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="R78" t="n">
-        <v>45</v>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -6170,8 +7427,10 @@
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="b">
-        <v>0</v>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6183,31 +7442,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K79" t="n">
-        <v>28</v>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>a3:v1000011:r1000025:block:1001588:1:0</t>
         </is>
       </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>1</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="R79" t="n">
-        <v>12.6</v>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -6242,8 +7515,10 @@
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="b">
-        <v>0</v>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6255,28 +7530,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K80" t="n">
-        <v>21</v>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>a3:v1000011:r1000025:block:1001605:1:0|a3:v1000011:r1000025:block:1001606:1:0</t>
         </is>
       </c>
-      <c r="M80" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R80" t="n">
-        <v>11.1</v>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -6311,8 +7599,10 @@
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="b">
-        <v>1</v>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6324,28 +7614,41 @@
           <t>E2|E6</t>
         </is>
       </c>
-      <c r="K81" t="n">
-        <v>38</v>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>a3:v1000012:r1000026:block:1001645:1:0|a3:v1000012:r1000026:block:1001646:1:0|a3:v1000012:r1000026:block:1001647:1:0</t>
         </is>
       </c>
-      <c r="M81" t="n">
-        <v>1</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="R81" t="n">
-        <v>100.1</v>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>35.2</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>100.1</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -6380,8 +7683,10 @@
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="b">
-        <v>0</v>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6393,28 +7698,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K82" t="n">
-        <v>19</v>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>a3:v1000012:r1000026:block:1001654:1:0</t>
         </is>
       </c>
-      <c r="M82" t="n">
-        <v>1</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>101</v>
-      </c>
-      <c r="R82" t="n">
-        <v>8.5</v>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -6449,8 +7767,10 @@
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="b">
-        <v>0</v>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6462,28 +7782,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K83" t="n">
-        <v>18</v>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>a3:v1000013:r1000022:block:1001429:1:0</t>
         </is>
       </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R83" t="n">
-        <v>8.199999999999999</v>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -6518,8 +7851,10 @@
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="b">
-        <v>1</v>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6532,28 +7867,41 @@
           <t>E3|E4</t>
         </is>
       </c>
-      <c r="K84" t="n">
-        <v>46</v>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>a3:v1000013:r1000022:block:1001431:1:0|a3:v1000013:r1000022:block:1001432:1:0|a3:v1000013:r1000022:block:1001433:1:0</t>
         </is>
       </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="R84" t="n">
-        <v>59.2</v>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>33.1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -6588,8 +7936,10 @@
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="b">
-        <v>1</v>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6602,31 +7952,45 @@
           <t>E3|E1</t>
         </is>
       </c>
-      <c r="K85" t="n">
-        <v>25</v>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>a3:v1000014:r1000084:block:1003639:1:0|a3:v1000014:r1000084:block:1003642:1:0</t>
         </is>
       </c>
-      <c r="M85" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" t="n">
-        <v>2</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P85" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="R85" t="n">
-        <v>44</v>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>84.1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -6661,8 +8025,10 @@
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="b">
-        <v>1</v>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6675,28 +8041,41 @@
           <t>E1|E5</t>
         </is>
       </c>
-      <c r="K86" t="n">
-        <v>27</v>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>a3:v1000014:r1000084:block:1003662:1:0</t>
         </is>
       </c>
-      <c r="M86" t="n">
-        <v>1</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="R86" t="n">
-        <v>68.2</v>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>64.3</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>68.2</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -6731,8 +8110,10 @@
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="b">
-        <v>0</v>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6745,31 +8126,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K87" t="n">
-        <v>25</v>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001808:1:0</t>
         </is>
       </c>
-      <c r="M87" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="P87" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="R87" t="n">
-        <v>14.6</v>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -6804,8 +8199,10 @@
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="b">
-        <v>0</v>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6819,31 +8216,45 @@
           <t>E3</t>
         </is>
       </c>
-      <c r="K88" t="n">
-        <v>20</v>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001808:1:0|a3:v1000015:r1000028:block:1001810:1:0</t>
         </is>
       </c>
-      <c r="M88" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>3</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P88" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="R88" t="n">
-        <v>17.5</v>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -6878,8 +8289,10 @@
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="b">
-        <v>1</v>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6893,31 +8306,45 @@
           <t>E8|E9</t>
         </is>
       </c>
-      <c r="K89" t="n">
-        <v>77</v>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001793:1:0</t>
         </is>
       </c>
-      <c r="M89" t="n">
-        <v>1</v>
-      </c>
-      <c r="N89" t="n">
-        <v>1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="R89" t="n">
-        <v>166.5</v>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>166.5</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -6952,8 +8379,10 @@
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="b">
-        <v>0</v>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6966,31 +8395,45 @@
           <t>E2</t>
         </is>
       </c>
-      <c r="K90" t="n">
-        <v>26</v>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>a3:v1000016:r1000029:block:1001835:1:0|a3:v1000016:r1000029:block:1001836:1:0</t>
         </is>
       </c>
-      <c r="M90" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N90" t="n">
-        <v>4</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1</v>
-      </c>
-      <c r="P90" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>174.4</v>
-      </c>
-      <c r="R90" t="n">
-        <v>15.6</v>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>174.4</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -7025,8 +8468,10 @@
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="b">
-        <v>0</v>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -7039,28 +8484,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K91" t="n">
-        <v>16</v>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>a3:v1000016:r1000029:block:1001851:1:0</t>
         </is>
       </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="R91" t="n">
-        <v>18.6</v>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -7095,8 +8553,10 @@
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="b">
-        <v>0</v>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -7109,28 +8569,41 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K92" t="n">
-        <v>30</v>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>a3:v1000016:r1000029:block:1001849:1:0</t>
         </is>
       </c>
-      <c r="M92" t="n">
-        <v>1</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>40</v>
-      </c>
-      <c r="R92" t="n">
-        <v>69.8</v>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>69.8</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -7165,8 +8638,10 @@
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="b">
-        <v>0</v>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -7180,31 +8655,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K93" t="n">
-        <v>20</v>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>a3:v1000017:r1000081:block:1003443:1:0</t>
         </is>
       </c>
-      <c r="M93" t="n">
-        <v>1</v>
-      </c>
-      <c r="N93" t="n">
-        <v>2</v>
-      </c>
-      <c r="O93" t="n">
-        <v>1</v>
-      </c>
-      <c r="P93" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="R93" t="n">
-        <v>19</v>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -7239,8 +8728,10 @@
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" t="b">
-        <v>0</v>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7252,31 +8743,45 @@
           <t>E1|E3</t>
         </is>
       </c>
-      <c r="K94" t="n">
-        <v>23</v>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>a3:v1000017:r1000081:block:1003450:1:0</t>
         </is>
       </c>
-      <c r="M94" t="n">
-        <v>1</v>
-      </c>
-      <c r="N94" t="n">
-        <v>2</v>
-      </c>
-      <c r="O94" t="n">
-        <v>1</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="R94" t="n">
-        <v>14.8</v>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -7311,8 +8816,10 @@
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="b">
-        <v>0</v>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7324,31 +8831,45 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="K95" t="n">
-        <v>20</v>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>a3:v1000017:r1000081:block:1003483:1:0|a3:v1000017:r1000081:block:1003487:1:0</t>
         </is>
       </c>
-      <c r="M95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" t="n">
-        <v>2</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="R95" t="n">
-        <v>14.3</v>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>39.2</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -7383,8 +8904,10 @@
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="b">
-        <v>1</v>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7397,31 +8920,45 @@
           <t>E17|E9</t>
         </is>
       </c>
-      <c r="K96" t="n">
-        <v>60</v>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>a3:v1000018:r1000031:block:1001991:1:0</t>
         </is>
       </c>
-      <c r="M96" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" t="n">
-        <v>1</v>
-      </c>
-      <c r="O96" t="n">
-        <v>1</v>
-      </c>
-      <c r="P96" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="R96" t="n">
-        <v>128.8</v>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -7456,8 +8993,10 @@
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="b">
-        <v>1</v>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7470,28 +9009,41 @@
           <t>E32|E1</t>
         </is>
       </c>
-      <c r="K97" t="n">
-        <v>41</v>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>a3:v1000018:r1000031:block:1001959:1:0|a3:v1000018:r1000031:block:1001978:1:0</t>
         </is>
       </c>
-      <c r="M97" t="n">
-        <v>1</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="R97" t="n">
-        <v>122.6</v>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>147.4</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>122.6</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -7530,8 +9082,10 @@
           <t>gateway_unavailable</t>
         </is>
       </c>
-      <c r="H98" t="b">
-        <v>0</v>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7539,28 +9093,41 @@
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="n">
-        <v>9</v>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>a3:v1000019:r1000041:block:1002799:1:0</t>
         </is>
       </c>
-      <c r="M98" t="n">
-        <v>1</v>
-      </c>
-      <c r="N98" t="n">
-        <v>2</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>140</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0.7</v>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -7599,8 +9166,10 @@
           <t>gateway_unavailable</t>
         </is>
       </c>
-      <c r="H99" t="b">
-        <v>0</v>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7608,28 +9177,41 @@
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="n">
-        <v>12</v>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>a3:v1000019:r1000041:block:1002805:1:0|a3:v1000019:r1000041:block:1002806:1:0</t>
         </is>
       </c>
-      <c r="M99" t="n">
-        <v>1</v>
-      </c>
-      <c r="N99" t="n">
-        <v>4</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.4</v>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -7668,8 +9250,10 @@
           <t>gateway_unavailable</t>
         </is>
       </c>
-      <c r="H100" t="b">
-        <v>0</v>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7677,28 +9261,41 @@
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="n">
-        <v>17</v>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001808:1:0|a3:v1000015:r1000028:block:1001810:1:0|a3:v1000017:r1000081:block:1003483:1:0|a3:v1000017:r1000081:block:1003484:1:0</t>
         </is>
       </c>
-      <c r="M100" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N100" t="n">
-        <v>4</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0.6</v>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -7737,8 +9334,10 @@
           <t>gateway_unavailable</t>
         </is>
       </c>
-      <c r="H101" t="b">
-        <v>0</v>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7746,28 +9345,41 @@
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="n">
-        <v>34</v>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001545:1:0|a3:v1000001:r1000024:block:1001546:1:0|a3:v1000014:r1000084:block:1003639:1:0</t>
         </is>
       </c>
-      <c r="M101" t="n">
-        <v>1</v>
-      </c>
-      <c r="N101" t="n">
-        <v>1</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.5</v>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7781,7 +9393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,7 +9496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7912,8 +9524,10 @@
           <t>response_rejected</t>
         </is>
       </c>
-      <c r="H2" t="b">
-        <v>0</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7921,28 +9535,41 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>33</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>a3:v1000002:r1000035:block:1002153:1:0|a3:v1000002:r1000035:block:1002154:1:0</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>59.8</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>46.6</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -7953,7 +9580,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7981,8 +9608,10 @@
           <t>gateway_unavailable</t>
         </is>
       </c>
-      <c r="H3" t="b">
-        <v>0</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -7990,28 +9619,41 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>9</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>a3:v1000019:r1000041:block:1002799:1:0</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>140</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.7</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -8022,7 +9664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8050,8 +9692,10 @@
           <t>gateway_unavailable</t>
         </is>
       </c>
-      <c r="H4" t="b">
-        <v>0</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -8059,28 +9703,41 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>12</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>a3:v1000019:r1000041:block:1002805:1:0|a3:v1000019:r1000041:block:1002806:1:0</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.4</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -8091,7 +9748,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8119,8 +9776,10 @@
           <t>gateway_unavailable</t>
         </is>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -8128,28 +9787,41 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>17</v>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>a3:v1000015:r1000028:block:1001808:1:0|a3:v1000015:r1000028:block:1001810:1:0|a3:v1000017:r1000081:block:1003483:1:0|a3:v1000017:r1000081:block:1003484:1:0</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.6</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -8160,7 +9832,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8188,8 +9860,10 @@
           <t>gateway_unavailable</t>
         </is>
       </c>
-      <c r="H6" t="b">
-        <v>0</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8197,373 +9871,41 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>34</v>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>a3:v1000001:r1000024:block:1001545:1:0|a3:v1000001:r1000024:block:1001546:1:0|a3:v1000014:r1000084:block:1003639:1:0</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P007</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>procedure|condition</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Khi điều chỉnh khe hở bugi Iridium Power, dụng cụ không được chạm vào những bộ phận nào và phải kiểm tra lại bằng gì?</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Không được chạm điện cực trung tâm iridium hoặc phần sứ; kiểm tra lại bằng dụng cụ đo khe hở đã hiệu chuẩn.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>response_rejected</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>33</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>a3:v1000002:r1000035:block:1002153:1:0|a3:v1000002:r1000035:block:1002154:1:0</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>64.59999999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P047</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>table|comparison</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Trong bảng Conventional &amp; Designer Wiper Blades, chiều dài 14 inch và 26 inch tương ứng bao nhiêu mm?</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>14 inch tương ứng 355 mm; 26 inch tương ứng 650 mm.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>gateway_unavailable</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>a3:v1000019:r1000041:block:1002799:1:0</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>140</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P048</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>table|identifier</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Trong bảng Rear Wiper Blades, cỡ 12 inch/300 mm liệt kê những mã sản phẩm nào?</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>160-5512, 160-5612, 160-5712 và 160-5912.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>gateway_unavailable</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>a3:v1000019:r1000041:block:1002805:1:0|a3:v1000019:r1000041:block:1002806:1:0</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P049</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>multi_document|table|comparison|footnote|condition</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>So sánh LPH-040A1 và VS-050S2 về tầm với, tải trọng tối đa và chu kỳ. Hai giá trị chu kỳ có được đo ở cùng tải không?</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LPH: 400 mm, tải tối đa 3 kg, chu kỳ 0,45 s đo với tải 2 kg. VS-050S2: 520 mm, tải tối đa 4 kg, chu kỳ 0,35 s đo với tải 1 kg. Cả hai nêu khoảng cách 300 mm, độ cao 25 mm nhưng tải thử khác nhau, nên không coi đây là so sánh chu kỳ cùng tải.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>gateway_unavailable</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>17</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>a3:v1000015:r1000028:block:1001808:1:0|a3:v1000015:r1000028:block:1001810:1:0|a3:v1000017:r1000081:block:1003483:1:0|a3:v1000017:r1000081:block:1003484:1:0</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P050</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>multi_document|comparison|attribute_leakage</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Trong tài liệu Protective Box Light và Dual-arm Control, RC8A đóng vai trò gì? Tên robot tương thích với Dual-arm Control là gì?</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RC8A là controller: được liệt kê là controller được hỗ trợ bởi Protective Box Light và controller tương thích với Dual-arm Control. Robot của Dual-arm Control là HSR Series và HS-A1 Series; không được gán RC8A thành tên robot.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>source_excerpt</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>gateway_unavailable</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Chưa tổng hợp được; bạn có thể đối chiếu các đoạn nguồn bên dưới.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>34</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>a3:v1000001:r1000024:block:1001545:1:0|a3:v1000001:r1000024:block:1001546:1:0|a3:v1000014:r1000084:block:1003639:1:0</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.5</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
     </row>
   </sheetData>
